--- a/program/workspace_variables.xlsx
+++ b/program/workspace_variables.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="740" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1036" uniqueCount="155">
   <si>
     <t>VariableName</t>
   </si>
@@ -488,6 +488,17 @@
   </si>
   <si>
     <t xml:space="preserve">com.hummeling.if97.IF97@5c45d770
+</t>
+  </si>
+  <si>
+    <t>C:\Users\Palych\Desktop\PAROGENA\program\ConstructionResults.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">com.hummeling.if97.IF97@10f7f7de
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">com.hummeling.if97.IF97@176b75f7
 </t>
   </si>
 </sst>
@@ -562,7 +573,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>0.00016069954808121929</v>
+        <v>0.00016368775303902689</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +589,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>4539</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="6">
@@ -594,7 +605,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>4539</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="8">
@@ -626,7 +637,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>5842.338817094208</v>
+        <v>5942.3575445192737</v>
       </c>
     </row>
     <row r="12">
@@ -642,7 +653,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>6251.3025342908031</v>
+        <v>6358.3225726356232</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +661,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>2.1351258250241534</v>
+        <v>2.1217013868950003</v>
       </c>
     </row>
     <row r="15">
@@ -658,7 +669,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>3912.5123933511322</v>
+        <v>3870.7345944850927</v>
       </c>
     </row>
     <row r="16">
@@ -674,7 +685,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>11423</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="18">
@@ -698,7 +709,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>3202</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +717,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>2988.5</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="22">
@@ -714,7 +725,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>12.645223440969783</v>
+        <v>12.808498462409087</v>
       </c>
     </row>
     <row r="23">
@@ -722,7 +733,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>6.4421487464567369</v>
+        <v>6.6399812870855284</v>
       </c>
     </row>
     <row r="24">
@@ -730,7 +741,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>9607</v>
+        <v>9794</v>
       </c>
     </row>
     <row r="25">
@@ -738,7 +749,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>2.2142226119867003</v>
+        <v>2.3186388823010962</v>
       </c>
     </row>
     <row r="26">
@@ -746,7 +757,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>7.7341860937132605</v>
+        <v>7.9257398747473076</v>
       </c>
     </row>
     <row r="27">
@@ -762,7 +773,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>428.91108665444909</v>
+        <v>431.59795252960487</v>
       </c>
     </row>
     <row r="29">
@@ -770,7 +781,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>0.8569455697049343</v>
+        <v>0.86537293732830123</v>
       </c>
     </row>
     <row r="30">
@@ -794,7 +805,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>2039.5</v>
+        <v>2028.5</v>
       </c>
     </row>
     <row r="33">
@@ -810,7 +821,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>1052.25</v>
+        <v>1046.75</v>
       </c>
     </row>
     <row r="35">
@@ -826,7 +837,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>2.7000000000000002e-05</v>
+        <v>3.0000000000000004e-05</v>
       </c>
     </row>
     <row r="37">
@@ -834,7 +845,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>265291.05477820878</v>
+        <v>265967.34772368631</v>
       </c>
     </row>
     <row r="38">
@@ -874,7 +885,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>2105</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="43">
@@ -890,7 +901,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>904.75</v>
+        <v>899.25</v>
       </c>
     </row>
     <row r="45">
@@ -898,7 +909,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>18646.819907509853</v>
+        <v>18650.921991806797</v>
       </c>
     </row>
     <row r="46">
@@ -906,7 +917,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>24556.371163244636</v>
+        <v>24266.311110830855</v>
       </c>
     </row>
     <row r="47">
@@ -922,7 +933,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="49">
@@ -946,7 +957,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>5.3936293173356828</v>
+        <v>5.4518440967986503</v>
       </c>
     </row>
     <row r="52">
@@ -954,7 +965,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>2988.5</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="53">
@@ -1018,7 +1029,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>18.352059925093634</v>
+        <v>17.954394509630287</v>
       </c>
     </row>
     <row r="61">
@@ -1090,7 +1101,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -1098,7 +1109,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>0.0077648792858207938</v>
+        <v>0.0077316570854861948</v>
       </c>
     </row>
     <row r="71">
@@ -1130,7 +1141,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75">
@@ -1178,7 +1189,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="0">
-        <v>2889</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="81">
@@ -1218,7 +1229,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="86">
@@ -1234,7 +1245,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="0">
-        <v>4822.0498435741065</v>
+        <v>4740.8875632297768</v>
       </c>
     </row>
     <row r="88">
@@ -1242,7 +1253,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="0">
-        <v>5387.8255712524624</v>
+        <v>5293.8941239150363</v>
       </c>
     </row>
     <row r="89">
@@ -1250,7 +1261,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="0">
-        <v>4256.2741158957506</v>
+        <v>4187.8810025445182</v>
       </c>
     </row>
     <row r="90">
@@ -1258,7 +1269,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="0">
-        <v>0.56517228474656778</v>
+        <v>0.561777423809389</v>
       </c>
     </row>
     <row r="91">
@@ -1290,7 +1301,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="0">
-        <v>8.9795174462013212e-05</v>
+        <v>8.9171108112230286e-05</v>
       </c>
     </row>
     <row r="95">
@@ -1298,7 +1309,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="0">
-        <v>16080</v>
+        <v>15960</v>
       </c>
     </row>
     <row r="96">
@@ -1322,7 +1333,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99">
@@ -1330,7 +1341,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="0">
-        <v>134.05000000000001</v>
+        <v>133.20833333333334</v>
       </c>
     </row>
     <row r="100">
@@ -1346,7 +1357,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="0">
-        <v>16086</v>
+        <v>15985</v>
       </c>
     </row>
     <row r="102">
@@ -1362,7 +1373,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="0">
-        <v>1.2250695760236232e-07</v>
+        <v>1.2219545097605092e-07</v>
       </c>
     </row>
     <row r="104">
@@ -1386,7 +1397,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="0">
-        <v>146.00181056805232</v>
+        <v>128.57521889803388</v>
       </c>
     </row>
     <row r="107">
@@ -1402,7 +1413,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="0">
-        <v>101136.54511943935</v>
+        <v>99434.266442461434</v>
       </c>
     </row>
     <row r="109">
@@ -1410,7 +1421,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="0">
-        <v>204737.37170759356</v>
+        <v>201167.97670877137</v>
       </c>
     </row>
     <row r="110">
@@ -1426,7 +1437,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="0">
-        <v>42562.741158957506</v>
+        <v>41878.810025445186</v>
       </c>
     </row>
     <row r="112">
@@ -1434,7 +1445,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="0">
-        <v>49050.981335950491</v>
+        <v>48138.536574912956</v>
       </c>
     </row>
     <row r="113">
@@ -1450,7 +1461,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="0">
-        <v>732.98020144679254</v>
+        <v>729.74163440590701</v>
       </c>
     </row>
     <row r="115">
@@ -1506,7 +1517,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="0">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="122">
@@ -1570,7 +1581,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="0">
-        <v>2988.5</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="130">

--- a/program/workspace_variables.xlsx
+++ b/program/workspace_variables.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1036" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1184" uniqueCount="156">
   <si>
     <t>VariableName</t>
   </si>
@@ -499,6 +499,10 @@
   </si>
   <si>
     <t xml:space="preserve">com.hummeling.if97.IF97@176b75f7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">com.hummeling.if97.IF97@662706a7
 </t>
   </si>
 </sst>
@@ -1229,7 +1233,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86">

--- a/program/workspace_variables.xlsx
+++ b/program/workspace_variables.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1184" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1332" uniqueCount="157">
   <si>
     <t>VariableName</t>
   </si>
@@ -503,6 +503,10 @@
   </si>
   <si>
     <t xml:space="preserve">com.hummeling.if97.IF97@662706a7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">com.hummeling.if97.IF97@5117dd67
 </t>
   </si>
 </sst>
@@ -1145,7 +1149,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75">
@@ -1233,7 +1237,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="86">

--- a/program/workspace_variables.xlsx
+++ b/program/workspace_variables.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1332" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1506" uniqueCount="189">
   <si>
     <t>VariableName</t>
   </si>
@@ -507,6 +507,113 @@
   </si>
   <si>
     <t xml:space="preserve">com.hummeling.if97.IF97@5117dd67
+</t>
+  </si>
+  <si>
+    <t>A_gk</t>
+  </si>
+  <si>
+    <t>A_hk</t>
+  </si>
+  <si>
+    <t>S_k</t>
+  </si>
+  <si>
+    <t>S_pto</t>
+  </si>
+  <si>
+    <t>deltaE</t>
+  </si>
+  <si>
+    <t>deltap1_pg</t>
+  </si>
+  <si>
+    <t>deltap_gk</t>
+  </si>
+  <si>
+    <t>deltap_hk</t>
+  </si>
+  <si>
+    <t>deltap_kol</t>
+  </si>
+  <si>
+    <t>deltapm_in</t>
+  </si>
+  <si>
+    <t>deltapm_out</t>
+  </si>
+  <si>
+    <t>deltapm_phi</t>
+  </si>
+  <si>
+    <t>deltaptr_L</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>ksim_in</t>
+  </si>
+  <si>
+    <t>ksim_out</t>
+  </si>
+  <si>
+    <t>ksim_phi</t>
+  </si>
+  <si>
+    <t>lambda</t>
+  </si>
+  <si>
+    <t>res2</t>
+  </si>
+  <si>
+    <t>rho1_g</t>
+  </si>
+  <si>
+    <t>rho1_h</t>
+  </si>
+  <si>
+    <t>w1_g</t>
+  </si>
+  <si>
+    <t>w1_h</t>
+  </si>
+  <si>
+    <t>w1_in</t>
+  </si>
+  <si>
+    <t>w1_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  &lt;a href="matlab:helpPopup('MException')" style="font-weight:bold"&gt;MException&lt;/a&gt; with properties:
+    identifier: ''
+       message: 'Файл "HydraulicResults.xlsx" уже открыт в Excel. Пожалуйста, закройте его и запустите скрипт снова.'
+         cause: {}
+         stack: [3×1 struct]
+    Correction: []
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {[2.8994]}
+</t>
+  </si>
+  <si>
+    <t>HydraulicResults.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\user\Desktop\PAROGENA\program\HydraulicResults.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {["Δp_гк"]}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    names: {8×1 cell}
+    units: [8×1 string]
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {'кПа'}
 </t>
   </si>
 </sst>
@@ -553,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="true"/>
@@ -578,39 +685,39 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="B3" s="0">
-        <v>0.00016368775303902689</v>
+        <v>0.74905897234104291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="B4" s="0">
-        <v>850</v>
+        <v>2.4150982872350713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" s="0">
-        <v>4517</v>
+        <v>0.00016368775303902689</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="0">
-        <v>3706</v>
+        <v>850</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="0">
         <v>4517</v>
@@ -618,1017 +725,1217 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="0">
-        <v>320</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="0">
-        <v>2.2400000000000002</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="0">
-        <v>322.24000000000001</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="0">
-        <v>5942.3575445192737</v>
+        <v>2.2400000000000002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="0">
-        <v>0.00013273228961416879</v>
+        <v>322.24000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="0">
-        <v>6358.3225726356232</v>
+        <v>5942.3575445192737</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="0">
-        <v>2.1217013868950003</v>
+        <v>0.00013273228961416879</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="0">
-        <v>3870.7345944850927</v>
+        <v>6358.3225726356232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="0">
-        <v>1.0700000000000001</v>
+        <v>2.1217013868950003</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="0">
-        <v>11600</v>
+        <v>3870.7345944850927</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="0">
-        <v>3630</v>
+        <v>1.0700000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="0">
-        <v>3630</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="0">
-        <v>3265</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="0">
-        <v>3082</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="0">
-        <v>12.808498462409087</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="0">
-        <v>6.6399812870855284</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="0">
-        <v>9794</v>
+        <v>12.808498462409087</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="0">
-        <v>2.3186388823010962</v>
+        <v>6.6399812870855284</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="0">
-        <v>7.9257398747473076</v>
+        <v>9794</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>135</v>
+        <v>24</v>
+      </c>
+      <c r="B27" s="0">
+        <v>2.3186388823010962</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="0">
-        <v>431.59795252960487</v>
+        <v>7.9257398747473076</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0">
-        <v>0.86537293732830123</v>
+        <v>26</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="0">
-        <v>590873.96337810031</v>
+        <v>431.59795252960487</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="0">
-        <v>582010.85392742884</v>
+        <v>0.86537293732830123</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" s="0">
-        <v>2028.5</v>
+        <v>590873.96337810031</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33" s="0">
-        <v>65</v>
+        <v>582010.85392742884</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34" s="0">
-        <v>1046.75</v>
+        <v>2028.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35" s="0">
-        <v>8.0071100712708016e-05</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="0">
-        <v>3.0000000000000004e-05</v>
+        <v>1046.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="0">
-        <v>265967.34772368631</v>
+        <v>8.0071100712708016e-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="0">
-        <v>24</v>
+        <v>3.0000000000000004e-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39" s="0">
-        <v>1650</v>
+        <v>265967.34772368631</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" s="0">
-        <v>21.600000000000001</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" s="0">
-        <v>21.600000000000001</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="0">
-        <v>2094</v>
+        <v>21.600000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43" s="0">
-        <v>3</v>
+        <v>21.600000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="0">
-        <v>899.25</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
       <c r="B45" s="0">
-        <v>18650.921991806797</v>
+        <v>0.52810172506844411</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="B46" s="0">
-        <v>24266.311110830855</v>
+        <v>2.1184073422421332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B47" s="0">
-        <v>0.69999999999999996</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B48" s="0">
-        <v>903</v>
+        <v>899.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B49" s="0">
-        <v>130</v>
+        <v>18650.921991806797</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B50" s="0">
-        <v>230</v>
+        <v>24266.311110830855</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" s="0">
-        <v>5.4518440967986503</v>
+        <v>0.69999999999999996</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B52" s="0">
-        <v>3082</v>
+        <v>903</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B53" s="0">
-        <v>1110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" s="0">
-        <v>16</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B55" s="0">
-        <v>374</v>
+        <v>5.4518440967986503</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" s="0">
-        <v>320</v>
+        <v>27.689971562770058</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B57" s="0">
-        <v>13</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="0" t="s">
-        <v>136</v>
+        <v>53</v>
+      </c>
+      <c r="B58" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="0" t="s">
-        <v>137</v>
+        <v>54</v>
+      </c>
+      <c r="B59" s="0">
+        <v>306</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B60" s="0">
-        <v>17.954394509630287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B61" s="0">
-        <v>140</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" s="0">
-        <v>1.5</v>
+        <v>57</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="0">
-        <v>10</v>
+        <v>58</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B64" s="0">
-        <v>38</v>
+        <v>17.954394509630287</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>64</v>
+        <v>161</v>
       </c>
       <c r="B65" s="0">
-        <v>20.973766012438578</v>
+        <v>1.9999999999999999e-06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B66" s="0">
-        <v>10</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B67" s="0">
-        <v>1100</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="B68" s="0">
-        <v>820</v>
+        <v>27.689971562770058</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="B69" s="0">
-        <v>20</v>
+        <v>2.8994084775499269</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="B70" s="0">
-        <v>0.0077316570854861948</v>
+        <v>10.129170166955896</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="B71" s="0">
-        <v>0.98499999999999999</v>
+        <v>4.8198411262706458</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" s="0" t="s">
-        <v>138</v>
+        <v>166</v>
+      </c>
+      <c r="B72" s="0">
+        <v>1.1949826974474691</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B73" s="0" t="s">
-        <v>139</v>
+        <v>167</v>
+      </c>
+      <c r="B73" s="0">
+        <v>2.4262672413052089</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="B74" s="0" t="s">
-        <v>140</v>
+        <v>168</v>
+      </c>
+      <c r="B74" s="0">
+        <v>1.1402213037592297</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="B75" s="0">
-        <v>2784.7761786896572</v>
+        <v>18.108659193987506</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B76" s="0">
-        <v>2787.9615080909671</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B77" s="0">
-        <v>1195.2968074360222</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B78" s="0">
-        <v>967.58623417923957</v>
+        <v>20.973766012438578</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B79" s="0">
-        <v>450</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B80" s="0">
-        <v>2867</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B81" s="0">
-        <v>200</v>
+        <v>820</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B82" s="0">
-        <v>600</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="B83" s="0">
-        <v>400</v>
+        <v>0.0077316570854861948</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B84" s="0">
-        <v>28</v>
+        <v>0.98499999999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B86" s="0">
-        <v>5</v>
+        <v>72</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="B87" s="0">
-        <v>4740.8875632297768</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B88" s="0">
-        <v>5293.8941239150363</v>
+        <v>73</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B89" s="0">
-        <v>4187.8810025445182</v>
+        <v>2784.7761786896572</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B90" s="0">
-        <v>0.561777423809389</v>
+        <v>2787.9615080909671</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B91" s="0">
-        <v>18.733350567790264</v>
+        <v>1195.2968074360222</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="B92" s="0">
-        <v>6</v>
+        <v>967.58623417923957</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="B93" s="0" t="s">
-        <v>142</v>
+        <v>78</v>
+      </c>
+      <c r="B93" s="0">
+        <v>450</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B94" s="0">
-        <v>8.9171108112230286e-05</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B95" s="0">
-        <v>15960</v>
+        <v>200</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B96" s="0">
-        <v>120</v>
+        <v>600</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B97" s="0">
-        <v>119.26416555294584</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B98" s="0">
-        <v>133</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="B99" s="0">
-        <v>133.20833333333334</v>
+        <v>84</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B100" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B101" s="0">
-        <v>15985</v>
+        <v>4740.8875632297768</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B102" s="0" t="s">
-        <v>143</v>
+        <v>87</v>
+      </c>
+      <c r="B102" s="0">
+        <v>5293.8941239150363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B103" s="0">
-        <v>1.2219545097605092e-07</v>
+        <v>4187.8810025445182</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="B104" s="0">
-        <v>28</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="B105" s="0">
-        <v>6</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="B106" s="0">
-        <v>128.57521889803388</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="B107" s="0">
-        <v>56.770642684183777</v>
+        <v>0.01302478869680739</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B108" s="0">
-        <v>99434.266442461434</v>
+        <v>0.561777423809389</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B109" s="0">
-        <v>201167.97670877137</v>
+        <v>18.733350567790264</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B110" s="0">
-        <v>150000</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B111" s="0">
-        <v>41878.810025445186</v>
+        <v>92</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B112" s="0">
-        <v>48138.536574912956</v>
+        <v>8.9171108112230286e-05</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="B113" s="0" t="s">
-        <v>144</v>
+        <v>94</v>
+      </c>
+      <c r="B113" s="0">
+        <v>15960</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B114" s="0">
-        <v>729.74163440590701</v>
+        <v>120</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B115" s="0">
-        <v>29.083898089814753</v>
+        <v>119.26416555294584</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="B116" s="0">
-        <v>836.61325452890219</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B117" s="0">
-        <v>30</v>
+        <v>133.20833333333334</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B118" s="0">
-        <v>296</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B119" s="0">
-        <v>310</v>
+        <v>15985</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="B120" s="0">
-        <v>282</v>
+        <v>101</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B121" s="0">
-        <v>330</v>
+        <v>1.2219545097605092e-07</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B122" s="0">
-        <v>272</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B123" s="0">
-        <v>225</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B124" s="0">
-        <v>8</v>
+        <v>128.57521889803388</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B125" s="0">
-        <v>30</v>
+        <v>56.770642684183777</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="B126" s="0" t="s">
-        <v>145</v>
+        <v>107</v>
+      </c>
+      <c r="B126" s="0">
+        <v>99434.266442461434</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="B127" s="0" t="s">
-        <v>146</v>
+        <v>108</v>
+      </c>
+      <c r="B127" s="0">
+        <v>201167.97670877137</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B128" s="0">
-        <v>0.034383286480783065</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B129" s="0">
-        <v>3082</v>
+        <v>41878.810025445186</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B130" s="0">
-        <v>2.5</v>
+        <v>48138.536574912956</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="B131" s="0">
-        <v>10</v>
+        <v>112</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="B132" s="0">
-        <v>4.7999999999999998</v>
+        <v>175</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="B133" s="0" t="s">
-        <v>147</v>
+        <v>113</v>
+      </c>
+      <c r="B133" s="0">
+        <v>729.74163440590701</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B134" s="0">
+        <v>698.46754919527666</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B135" s="0">
+        <v>756.81877411383653</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B136" s="0">
+        <v>29.083898089814753</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B137" s="0">
+        <v>836.61325452890219</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B138" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B139" s="0">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B140" s="0">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B141" s="0">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B142" s="0">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B143" s="0">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B144" s="0">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="B145" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B146" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="B149" s="0">
+        <v>0.034383286480783065</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="B150" s="0">
+        <v>27.689971562770058</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B151" s="0">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B152" s="0">
+        <v>5.5417529403401353</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B153" s="0">
+        <v>5.5417529403401353</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B154" s="0">
+        <v>2.6159996851572069</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="B155" s="0">
+        <v>2.4143043900131018</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B156" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B157" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="B134" s="0">
+      <c r="B159" s="0">
         <v>0.998</v>
       </c>
     </row>

--- a/program/workspace_variables.xlsx
+++ b/program/workspace_variables.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1506" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1680" uniqueCount="190">
   <si>
     <t>VariableName</t>
   </si>
@@ -615,6 +615,9 @@
   <si>
     <t xml:space="preserve">    {'кПа'}
 </t>
+  </si>
+  <si>
+    <t>C:\Users\Palych\Desktop\PAROGENA\program\HydraulicResults.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1371,7 @@
         <v>73</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89">
@@ -1456,7 +1459,7 @@
         <v>84</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100">
